--- a/DAM_PreSchool_Pending_Work.xlsx
+++ b/DAM_PreSchool_Pending_Work.xlsx
@@ -38,7 +38,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -52,17 +52,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE06666"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -134,9 +129,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -571,12 +563,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Realtime announcements (parent view)</t>
+          <t>Parent announcements view</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -586,12 +578,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md / README_DASHBOARDS.md</t>
+          <t>app/(parent)/index.tsx:347 (verified in code)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Parents see announcements but no Supabase realtime subscription yet.</t>
+          <t>Announcements table + admin posting exist, but the parent 'Notices' button is a hardcoded stub Alert. Needs DB fetch + display first; realtime is a follow-up.</t>
         </is>
       </c>
     </row>
@@ -609,7 +601,7 @@
           <t>Parent–Teacher chat</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -644,12 +636,12 @@
           <t>Unread message indicators</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -679,12 +671,12 @@
           <t>File attachments in messages/announcements</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -714,7 +706,7 @@
           <t>Online fee payment integration</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -749,7 +741,7 @@
           <t>Admin fee collection / processing</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -784,12 +776,12 @@
           <t>Payment receipt PDF download</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -819,7 +811,7 @@
           <t>Reschedule request backend</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -854,7 +846,7 @@
           <t>Update appointment in backend on reschedule</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -889,12 +881,12 @@
           <t>Class assignment (assign teachers to classes)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -924,12 +916,12 @@
           <t>Holiday management (create/delete)</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -959,12 +951,12 @@
           <t>Reports analytics / charts</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -994,12 +986,12 @@
           <t>Admin profile editing</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1029,12 +1021,12 @@
           <t>'More' menu unrouted items</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1064,12 +1056,12 @@
           <t>Teacher student list from DB</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1099,7 +1091,7 @@
           <t>Principal routes to admin dashboard</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
@@ -1134,7 +1126,7 @@
           <t>Push notifications end-to-end</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
@@ -1169,7 +1161,7 @@
           <t>Google OAuth PKCE fix</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
@@ -1204,12 +1196,12 @@
           <t>Consolidate SQL scripts into migrations</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1239,12 +1231,12 @@
           <t>Error tracking service (Sentry/Bugsnag)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1274,12 +1266,12 @@
           <t>Offline support / caching</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1309,12 +1301,12 @@
           <t>Export reports (PDF/Excel)</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>

--- a/DAM_PreSchool_Pending_Work.xlsx
+++ b/DAM_PreSchool_Pending_Work.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Pending Work" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending Work'!$A$2:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pending Work'!$A$2:$G$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,12 +52,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE06666"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -68,11 +73,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB6D7A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Needs verification</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>app/(parent)/index.tsx:347 (verified in code)</t>
+          <t>app/(parent)/index.tsx (implemented this session)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Announcements table + admin posting exist, but the parent 'Notices' button is a hardcoded stub Alert. Needs DB fetch + display first; realtime is a follow-up.</t>
+          <t>DONE: 'Notices' button now opens a modal that fetches from announcements (audience-filtered) and shows title/body/attachment/date. Verify on device. Realtime live-update is the remaining follow-up (needs Realtime enabled on the table).</t>
         </is>
       </c>
     </row>
@@ -598,27 +598,27 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Parent–Teacher chat</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Realtime announcements (live update)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md</t>
+          <t>follow-up to parent announcements view</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Messaging UI exists for admin; parent&lt;-&gt;teacher channel not connected.</t>
+          <t>Notices refetch each time the modal opens. Optional: subscribe via supabase.channel(postgres_changes) so new notices appear without reopening; requires enabling Realtime on the announcements table in Supabase.</t>
         </is>
       </c>
     </row>
@@ -633,27 +633,27 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Unread message indicators</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Parent–Teacher chat</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>README_DASHBOARDS.md</t>
+          <t>PROGRESS_TRACKING.md</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>No unread badges on conversations.</t>
+          <t>Messaging UI exists for admin; parent&lt;-&gt;teacher channel not connected.</t>
         </is>
       </c>
     </row>
@@ -668,17 +668,17 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>File attachments in messages/announcements</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+          <t>Unread message indicators</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>No file sharing support yet.</t>
+          <t>No unread badges on conversations.</t>
         </is>
       </c>
     </row>
@@ -698,32 +698,32 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Fees</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Online fee payment integration</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>File attachments in messages/announcements</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md</t>
+          <t>README_DASHBOARDS.md</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Fees are view-only; no payment gateway wired.</t>
+          <t>No file sharing support yet.</t>
         </is>
       </c>
     </row>
@@ -738,10 +738,10 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Admin fee collection / processing</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+          <t>Online fee payment integration</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -758,7 +758,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>No way to record/collect payments from admin side.</t>
+          <t>Fees are view-only; no payment gateway wired.</t>
         </is>
       </c>
     </row>
@@ -773,27 +773,27 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Payment receipt PDF download</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Admin fee collection / processing</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>docs/PAYMENT_RECEIPT_FEATURE.md</t>
+          <t>PROGRESS_TRACKING.md</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Receipt screen exists; 'Download PDF' marked coming soon.</t>
+          <t>No way to record/collect payments from admin side.</t>
         </is>
       </c>
     </row>
@@ -803,32 +803,32 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Appointments</t>
+          <t>Fees</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Reschedule request backend</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>Payment receipt PDF download</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>.kiro/specs/parent-appointment-modals (task 8.8)</t>
+          <t>docs/PAYMENT_RECEIPT_FEATURE.md</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Reschedule details only logged; replace with real backend call.</t>
+          <t>Receipt screen exists; 'Download PDF' marked coming soon.</t>
         </is>
       </c>
     </row>
@@ -843,10 +843,10 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Update appointment in backend on reschedule</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+          <t>Reschedule request backend</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
@@ -858,12 +858,12 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>.kiro/specs/.../design.md (TODO)</t>
+          <t>.kiro/specs/parent-appointment-modals (task 8.8)</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Backend mutation not implemented.</t>
+          <t>Reschedule details only logged; replace with real backend call.</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>Appointments</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Class assignment (assign teachers to classes)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Update appointment in backend on reschedule</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md</t>
+          <t>.kiro/specs/.../design.md (TODO)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Admin cannot assign teachers to classes.</t>
+          <t>Backend mutation not implemented.</t>
         </is>
       </c>
     </row>
@@ -913,27 +913,27 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Holiday management (create/delete)</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Needs verification</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
+          <t>Class assignment (assign teachers to classes)</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md vs schema</t>
+          <t>PROGRESS_TRACKING.md</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Doc says view-only; holidays table + RLS exist — confirm admin CRUD UI.</t>
+          <t>Admin cannot assign teachers to classes.</t>
         </is>
       </c>
     </row>
@@ -948,27 +948,27 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Reports analytics / charts</t>
+          <t>Holiday management (create/delete)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
+          <t>Needs verification</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md</t>
+          <t>PROGRESS_TRACKING.md vs schema</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Reports screen present; charts not connected to data.</t>
+          <t>Doc says view-only; holidays table + RLS exist — confirm admin CRUD UI.</t>
         </is>
       </c>
     </row>
@@ -983,27 +983,27 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Admin profile editing</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+          <t>Reports analytics / charts</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>app/(dashboard)/admin-profile.tsx:169</t>
+          <t>PROGRESS_TRACKING.md</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>'Coming Soon' alert on edit profile.</t>
+          <t>Reports screen present; charts not connected to data.</t>
         </is>
       </c>
     </row>
@@ -1018,27 +1018,27 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>'More' menu unrouted items</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+          <t>Admin profile editing</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>app/(dashboard)/more.tsx:163</t>
+          <t>app/(dashboard)/admin-profile.tsx:169</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Menu items without a route show 'Coming Soon'.</t>
+          <t>'Coming Soon' alert on edit profile.</t>
         </is>
       </c>
     </row>
@@ -1048,32 +1048,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Teacher student list from DB</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Needs verification</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>'More' menu unrouted items</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md</t>
+          <t>app/(dashboard)/more.tsx:163</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Doc says not fetched from DB; verify against current teacher screens.</t>
+          <t>Menu items without a route show 'Coming Soon'.</t>
         </is>
       </c>
     </row>
@@ -1083,32 +1083,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Routing</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Principal routes to admin dashboard</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
+          <t>Teacher student list from DB</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>PROGRESS_TRACKING.md (known issue)</t>
+          <t>PROGRESS_TRACKING.md</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Doc flags principal landing on admin dashboard; verify auth-routing.ts handles principal.</t>
+          <t>Doc says not fetched from DB; verify against current teacher screens.</t>
         </is>
       </c>
     </row>
@@ -1118,15 +1118,15 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Routing</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Push notifications end-to-end</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
+          <t>Principal routes to admin dashboard</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>code: usePushNotifications.ts / send-push</t>
+          <t>PROGRESS_TRACKING.md (known issue)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>IMPLEMENTED since the doc was written. Verify delivery on a physical prod build via adb logcat.</t>
+          <t>Doc flags principal landing on admin dashboard; verify auth-routing.ts handles principal.</t>
         </is>
       </c>
     </row>
@@ -1153,15 +1153,15 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Google OAuth PKCE fix</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+          <t>Push notifications end-to-end</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Needs verification</t>
         </is>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>lib/supabase.ts / context/auth.tsx (this session)</t>
+          <t>code: usePushNotifications.ts / send-push</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>flowType:pkce + Linking.createURL added. Rebuild APK and confirm sign-in completes.</t>
+          <t>IMPLEMENTED since the doc was written. Verify delivery on a physical prod build via adb logcat.</t>
         </is>
       </c>
     </row>
@@ -1188,32 +1188,32 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Auth</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Consolidate SQL scripts into migrations</t>
+          <t>Google OAuth PKCE fix</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>Needs verification</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>supabase/*.sql</t>
+          <t>lib/supabase.ts / context/auth.tsx (this session)</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Dozens of ad-hoc fix_/debug_ scripts; no versioned migrations folder.</t>
+          <t>flowType:pkce + Linking.createURL added. Rebuild APK and confirm sign-in completes.</t>
         </is>
       </c>
     </row>
@@ -1228,27 +1228,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Error tracking service (Sentry/Bugsnag)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
+          <t>Consolidate SQL scripts into migrations</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>utils/errorHandler.ts:146</t>
+          <t>supabase/*.sql</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>TODO: send errors to a tracking service.</t>
+          <t>Dozens of ad-hoc fix_/debug_ scripts; no versioned migrations folder.</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Offline support / caching</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
+          <t>Error tracking service (Sentry/Bugsnag)</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>README_DASHBOARDS.md</t>
+          <t>utils/errorHandler.ts:146</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>No offline caching for data fetches.</t>
+          <t>TODO: send errors to a tracking service.</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1298,67 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
+          <t>Offline support / caching</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>README_DASHBOARDS.md</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>No offline caching for data fetches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
           <t>Export reports (PDF/Excel)</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>README_DASHBOARDS.md</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Report export not implemented.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G24"/>
+  <autoFilter ref="A2:G25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
